--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Half &amp; Half</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>262.32</t>
-        </is>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="E2" t="n">
+        <v>262.32</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Dirty Chip - Cracked Pepper (2oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>36.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Dirty Chip - Funky Fusion Pot (2oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Dirty Chip - Jalapeno Hot (2oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E5" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Dirty Chip - Maui Onion Pot (2oz)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E6" t="n">
+        <v>39.98</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Dirty Chip - Mesquite Barbecue (2oz)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E7" t="n">
+        <v>39.98</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Dirty Chip - Sea Salted (2oz)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>19.99</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>99.95</t>
-        </is>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>99.95</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Dirty Chip - Sour Cream &amp; Onion (2oz)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>18.00</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>PKT Hot Sauce - Texas Pete</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>17.18</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>34.36</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>34.36</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Tractor - Farmers Punch</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Tractor - Lemonade</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Tractor - Peach Mango</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Tractor - Strawberry Dragon</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>23.19</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>23.19</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>Bagel - Plain GF</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>22.75</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22.75</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/US Foods/US Foods_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,6 +737,531 @@
         <v>22.75</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0877506</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Butter - Salted</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E16" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3791747</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Can - Roasted Red Pepper (Strips)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>49.22</v>
+      </c>
+      <c r="E17" t="n">
+        <v>98.44</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4886244</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Goat Cheese</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="E18" t="n">
+        <v>91.86</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1030192</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BBQ - Sauce</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>72.94</v>
+      </c>
+      <c r="E19" t="n">
+        <v>72.94</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0490508</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Brie</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="E20" t="n">
+        <v>53.88</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1025722</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Broccoli - FRZ</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="E21" t="n">
+        <v>135.27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7206874</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Can - Tomato (crushed)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="E22" t="n">
+        <v>65.31999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1027629</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cheddar - (Sliced)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="E23" t="n">
+        <v>349.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1035842</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Feta - Pail</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="E24" t="n">
+        <v>92.87</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1345057</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Blueberry</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="E25" t="n">
+        <v>76.72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3357597</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FRZ Fruit - Strawberry (Whole)</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="E26" t="n">
+        <v>43.74</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3737152</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Honey - Jug</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>102.73</v>
+      </c>
+      <c r="E27" t="n">
+        <v>102.73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6422273</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lemon Juice</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7722184</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Parmesan (Grated)</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="E29" t="n">
+        <v>59.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1028165</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pickle - Dill Chip</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="E30" t="n">
+        <v>34.09</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3275539</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sauerkraut</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="E31" t="n">
+        <v>77.40000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1132582</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sour Cream</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="E32" t="n">
+        <v>28.94</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1025103</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Swiss (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8255796</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tuna White Chunk (Pouch)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7529232</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Wrap - Wheat (10")</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>29.89</v>
+      </c>
+      <c r="E35" t="n">
+        <v>29.89</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6364494</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Yogurt - Greek (Bulk)</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>26.96</v>
+      </c>
+      <c r="E36" t="n">
+        <v>26.96</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4052171</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Apple Red - Fresh</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="E37" t="n">
+        <v>27.08</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>9546982</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Arugula - Fresh</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="E38" t="n">
+        <v>81.40000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2006567</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Potato - Chef</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>21</v>
+      </c>
+      <c r="E39" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1030194</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Bleach</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>26.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
